--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -8272,7 +8272,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -6392,7 +6392,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -8272,7 +8272,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -6392,7 +6392,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -6392,7 +6392,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -6392,7 +6392,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -6392,7 +6392,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -6392,7 +6392,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260521_212414.xlsx
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
